--- a/artfynd/A 21858-2026 artfynd.xlsx
+++ b/artfynd/A 21858-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>133573776</v>
       </c>
       <c r="B3" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133573760</v>
       </c>
       <c r="B4" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>133573740</v>
       </c>
       <c r="B5" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>133573725</v>
       </c>
       <c r="B6" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21858-2026 artfynd.xlsx
+++ b/artfynd/A 21858-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>123157339</v>
       </c>
       <c r="B2" t="n">
-        <v>57973</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -777,53 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573776</v>
+        <v>133573818</v>
       </c>
       <c r="B3" t="n">
-        <v>110152</v>
+        <v>8449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Solhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588266</v>
+        <v>588251</v>
       </c>
       <c r="R3" t="n">
-        <v>6398836</v>
+        <v>6398833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +858,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hål från björksplintborre noterade på liggande död björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133573760</v>
+        <v>133573740</v>
       </c>
       <c r="B4" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,7 +933,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588252</v>
+        <v>588250</v>
       </c>
       <c r="R4" t="n">
         <v>6398867</v>
@@ -1009,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133573740</v>
+        <v>133573760</v>
       </c>
       <c r="B5" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1049,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588250</v>
+        <v>588252</v>
       </c>
       <c r="R5" t="n">
         <v>6398867</v>
@@ -1125,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133573725</v>
+        <v>133573776</v>
       </c>
       <c r="B6" t="n">
-        <v>101396</v>
+        <v>110159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588283</v>
+        <v>588266</v>
       </c>
       <c r="R6" t="n">
-        <v>6398937</v>
+        <v>6398836</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133573818</v>
+        <v>133573725</v>
       </c>
       <c r="B7" t="n">
-        <v>8449</v>
+        <v>101403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,42 +1249,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Solhem, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588251</v>
+        <v>588283</v>
       </c>
       <c r="R7" t="n">
-        <v>6398833</v>
+        <v>6398937</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,11 +1327,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hål från björksplintborre noterade på liggande död björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
